--- a/model.xlsx
+++ b/model.xlsx
@@ -385,7 +385,7 @@
     <t xml:space="preserve">อัตราปรับบำนาญต่อปี</t>
   </si>
   <si>
-    <t xml:space="preserve">บำนาญข้าราชการไทยไม่มีกลไกปรับตามเงินเฟ้ออัตโนมัติ</t>
+    <t xml:space="preserve">ไทยไม่มีกลไกปรับอัตโนมัติ แต่ปรับเป็นระยะด้วยการออก พ.ร.ฎ. เงินช่วยค่าครองชีพผู้รับเบี้ยหวัดบำนาญ (ช.ค.บ.) แก้ไขมาแล้ว 17 ฉบับนับจาก พ.ศ. 2521 · สองครั้งหลังสุดยกเฉพาะพื้นขั้นต่ำ จาก 10,000 บาท (ฉบับที่ 16 พ.ศ. 2562) เป็น 11,000 บาท (ฉบับที่ 17 มีผล 1 พ.ค. 2567) ไม่ได้ยกทั้งฐาน · ตั้ง 1% ซึ่งต่ำกว่าเงินเฟ้อ ปรับเองได้</t>
   </si>
   <si>
     <t xml:space="preserve">เพดานบำนาญ (% ของเงินเดือนเฉลี่ย 60 เดือน)</t>
@@ -400,10 +400,10 @@
     <t xml:space="preserve">บำนาญ = เงินเดือนเฉลี่ย 60 เดือนสุดท้าย × เวลาราชการ ÷ 50</t>
   </si>
   <si>
-    <t xml:space="preserve">ช.ค.บ. — ประกันบำนาญขั้นต่ำ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ผู้รับบำนาญที่รวม ช.ค.บ. แล้วไม่ถึง 11,000 บาท/เดือน ให้ได้รับเพิ่มจนครบ</t>
+    <t xml:space="preserve">ช.ค.บ. — พื้นบำนาญขั้นต่ำ (ราคาปี 2569)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">พ.ร.ฎ. ฉบับที่ 17 มีผล 1 พ.ค. 2567 · แบบจำลองให้พื้นนี้โตตามเงินเฟ้อจนถึงปีเกษียณ เพราะในทางปฏิบัติถูกยกเป็นระยะ (10,000 ในปี 2562 เป็น 11,000 ในปี 2567 ≈ 1.9% ต่อปี)</t>
   </si>
   <si>
     <t xml:space="preserve">บำเหน็จดำรงชีพ ครั้งที่ 1 (อายุต่ำกว่า 65)</t>
@@ -508,7 +508,7 @@
     <t xml:space="preserve">บำนาญรายเดือน</t>
   </si>
   <si>
-    <t xml:space="preserve">ช.ค.บ. รายเดือน</t>
+    <t xml:space="preserve">ช.ค.บ. รายเดือน (พื้นโตตามเงินเฟ้อถึงปีเกษียณ)</t>
   </si>
   <si>
     <t xml:space="preserve">บำนาญ + ช.ค.บ. รายเดือน</t>
@@ -847,25 +847,25 @@
     <t xml:space="preserve">ข้อสรุปสำคัญ</t>
   </si>
   <si>
-    <t xml:space="preserve">• ที่เงินเฟ้อ 0% (คิดทุกอย่างเป็นราคาปี 2569) ต้นทุนกรณีระดับกลางอยู่ที่ราว 37 ล้านบาท</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• ที่เงินเฟ้อ 2% ตัวเลข 'เงินสดจ่ายจริง' พุ่งเป็น 65 ล้านบาท ทั้งที่สวัสดิการที่ได้รับเท่าเดิมทุกบาท</t>
+    <t xml:space="preserve">• ที่เงินเฟ้อ 0% (คิดทุกอย่างเป็นราคาปี 2569) ต้นทุนกรณีระดับกลางอยู่ที่ราว 40 ล้านบาท</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ที่เงินเฟ้อ 2% ตัวเลข 'เงินสดจ่ายจริง' พุ่งเป็น 67.5 ล้านบาท ทั้งที่สวัสดิการที่ได้รับเท่าเดิมทุกบาท</t>
   </si>
   <si>
     <t xml:space="preserve">• ตัวเลข 40 ล้านใกล้เคียงกับ 'ราคาปี 2569' ของกรณีระดับกลาง มากกว่าจะเป็นเงินสดที่จ่ายจริงในอนาคต</t>
   </si>
   <si>
-    <t xml:space="preserve">• ถ้าตีความว่าเป็นเงินสดสะสมจริง ตัวเลขที่ควรพูดถึงสำหรับคนระดับกลางคือราว 65 ล้าน</t>
-  </si>
-  <si>
     <t xml:space="preserve">• ค่ารักษาพยาบาลของบิดามารดา ในราคาปี 2569 คิดเป็นราว 40% ของค่ารักษาทั้งหมด ไม่ใช่ก้อนเล็ก</t>
   </si>
   <si>
     <t xml:space="preserve">• ที่ตัวเลขตัวเงินจริงของพ่อแม่ดูต่ำ เป็นเพราะพ่อแม่ป่วยในช่วงปีต้น ๆ ที่ค่าเงินยังไม่เฟ้อ ไม่ใช่เพราะรัฐดูแลพ่อแม่ถูกกว่า</t>
   </si>
   <si>
-    <t xml:space="preserve">• ค่าเฉลี่ยกลบความต่าง: ผู้น้อย 38.7 ล้าน ระดับสูง 95.4 ล้าน ต่างกัน 2.5 เท่า</t>
+    <t xml:space="preserve">• บำนาญไทยไม่มีกลไกปรับอัตโนมัติ แต่ปรับเป็นระยะผ่าน พ.ร.ฎ. ช.ค.บ. แบบจำลองตั้งไว้ 1% ต่อปี ถ้าตั้ง 0% ต้นทุนกรณีกลางจะลดจาก 67.5 เหลือ 65.4 ล้าน</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• ค่าเฉลี่ยกลบความต่าง: ผู้น้อย 39.8 ล้าน ระดับสูง 99.3 ล้าน ต่างกัน 2.5 เท่า</t>
   </si>
   <si>
     <t xml:space="preserve">ข้อมูลที่ใช้</t>
@@ -2506,12 +2506,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
         <v>118</v>
       </c>
       <c r="B41" s="16" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>119</v>
@@ -2539,7 +2539,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
         <v>124</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>160</v>
       </c>
       <c r="AA5" s="14" t="n">
-        <f aca="false">MAX(0,สมมติฐาน!$B$44-AA4)</f>
+        <f aca="false">MAX(0,สมมติฐาน!$B$44*(1+สมมติฐาน!$B$39)^(สมมติฐาน!$B$10-1)-AA4)</f>
         <v>0</v>
       </c>
     </row>
@@ -6508,7 +6508,7 @@
       </c>
       <c r="S48" s="26" t="n">
         <f aca="false">IF(D48="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A48-38-1))</f>
-        <v>575678.115283025</v>
+        <v>581434.896435856</v>
       </c>
       <c r="T48" s="26" t="n">
         <f aca="false">IF(C48=สมมติฐาน!$B$8,$AA$7,0)+IF(C48=65,$AA$9,0)+IF(A48=57,$AA$10+$AA$11,0)</f>
@@ -6516,11 +6516,11 @@
       </c>
       <c r="U48" s="26" t="n">
         <f aca="false">G48+H48+I48+J48+K48+L48+P48+Q48+R48+S48+T48</f>
-        <v>706889.472809649</v>
+        <v>712646.253962479</v>
       </c>
       <c r="V48" s="26" t="n">
         <f aca="false">U48/E48</f>
-        <v>326546.336167451</v>
+        <v>329205.670994016</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="S49" s="14" t="n">
         <f aca="false">IF(D49="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A49-38-1))</f>
-        <v>575678.115283025</v>
+        <v>587249.245400214</v>
       </c>
       <c r="T49" s="14" t="n">
         <f aca="false">IF(C49=สมมติฐาน!$B$8,$AA$7,0)+IF(C49=65,$AA$9,0)+IF(A49=57,$AA$10+$AA$11,0)</f>
@@ -6605,11 +6605,11 @@
       </c>
       <c r="U49" s="14" t="n">
         <f aca="false">G49+H49+I49+J49+K49+L49+P49+Q49+R49+S49+T49</f>
-        <v>712190.411653725</v>
+        <v>723761.541770913</v>
       </c>
       <c r="V49" s="14" t="n">
         <f aca="false">U49/E49</f>
-        <v>322544.211224799</v>
+        <v>327784.665147736</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="S50" s="26" t="n">
         <f aca="false">IF(D50="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A50-38-1))</f>
-        <v>575678.115283025</v>
+        <v>593121.737854217</v>
       </c>
       <c r="T50" s="26" t="n">
         <f aca="false">IF(C50=สมมติฐาน!$B$8,$AA$7,0)+IF(C50=65,$AA$9,0)+IF(A50=57,$AA$10+$AA$11,0)</f>
@@ -6694,11 +6694,11 @@
       </c>
       <c r="U50" s="26" t="n">
         <f aca="false">G50+H50+I50+J50+K50+L50+P50+Q50+R50+S50+T50</f>
-        <v>717705.508427101</v>
+        <v>735149.130998292</v>
       </c>
       <c r="V50" s="26" t="n">
         <f aca="false">U50/E50</f>
-        <v>318668.574208118</v>
+        <v>326413.720745963</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="S51" s="14" t="n">
         <f aca="false">IF(D51="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A51-38-1))</f>
-        <v>575678.115283025</v>
+        <v>599052.955232759</v>
       </c>
       <c r="T51" s="14" t="n">
         <f aca="false">IF(C51=สมมติฐาน!$B$8,$AA$7,0)+IF(C51=65,$AA$9,0)+IF(A51=57,$AA$10+$AA$11,0)</f>
@@ -6783,11 +6783,11 @@
       </c>
       <c r="U51" s="14" t="n">
         <f aca="false">G51+H51+I51+J51+K51+L51+P51+Q51+R51+S51+T51</f>
-        <v>723443.415110122</v>
+        <v>746818.255059855</v>
       </c>
       <c r="V51" s="14" t="n">
         <f aca="false">U51/E51</f>
-        <v>314917.905259754</v>
+        <v>325093.069590514</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="S52" s="26" t="n">
         <f aca="false">IF(D52="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A52-38-1))</f>
-        <v>575678.115283025</v>
+        <v>605043.484785086</v>
       </c>
       <c r="T52" s="26" t="n">
         <f aca="false">IF(C52=สมมติฐาน!$B$8,$AA$7,0)+IF(C52=65,$AA$9,0)+IF(A52=57,$AA$10+$AA$11,0)</f>
@@ -6872,11 +6872,11 @@
       </c>
       <c r="U52" s="26" t="n">
         <f aca="false">G52+H52+I52+J52+K52+L52+P52+Q52+R52+S52+T52</f>
-        <v>1029413.13322314</v>
+        <v>1058778.5027252</v>
       </c>
       <c r="V52" s="26" t="n">
         <f aca="false">U52/E52</f>
-        <v>439321.359528538</v>
+        <v>451853.581662046</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="S53" s="14" t="n">
         <f aca="false">IF(D53="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A53-38-1))</f>
-        <v>575678.115283025</v>
+        <v>611093.919632937</v>
       </c>
       <c r="T53" s="14" t="n">
         <f aca="false">IF(C53=สมมติฐาน!$B$8,$AA$7,0)+IF(C53=65,$AA$9,0)+IF(A53=57,$AA$10+$AA$11,0)</f>
@@ -6961,11 +6961,11 @@
       </c>
       <c r="U53" s="14" t="n">
         <f aca="false">G53+H53+I53+J53+K53+L53+P53+Q53+R53+S53+T53</f>
-        <v>735624.027947917</v>
+        <v>771039.832297828</v>
       </c>
       <c r="V53" s="14" t="n">
         <f aca="false">U53/E53</f>
-        <v>307785.636595986</v>
+        <v>322603.63529269</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="S54" s="26" t="n">
         <f aca="false">IF(D54="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A54-38-1))</f>
-        <v>575678.115283025</v>
+        <v>617204.858829266</v>
       </c>
       <c r="T54" s="26" t="n">
         <f aca="false">IF(C54=สมมติฐาน!$B$8,$AA$7,0)+IF(C54=65,$AA$9,0)+IF(A54=57,$AA$10+$AA$11,0)</f>
@@ -7050,11 +7050,11 @@
       </c>
       <c r="U54" s="26" t="n">
         <f aca="false">G54+H54+I54+J54+K54+L54+P54+Q54+R54+S54+T54</f>
-        <v>742085.842819578</v>
+        <v>783612.586365819</v>
       </c>
       <c r="V54" s="26" t="n">
         <f aca="false">U54/E54</f>
-        <v>304401.239912478</v>
+        <v>321435.377333796</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="S55" s="14" t="n">
         <f aca="false">IF(D55="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A55-38-1))</f>
-        <v>575678.115283025</v>
+        <v>623376.907417559</v>
       </c>
       <c r="T55" s="14" t="n">
         <f aca="false">IF(C55=สมมติฐาน!$B$8,$AA$7,0)+IF(C55=65,$AA$9,0)+IF(A55=57,$AA$10+$AA$11,0)</f>
@@ -7139,11 +7139,11 @@
       </c>
       <c r="U55" s="14" t="n">
         <f aca="false">G55+H55+I55+J55+K55+L55+P55+Q55+R55+S55+T55</f>
-        <v>748808.715012055</v>
+        <v>796507.507146589</v>
       </c>
       <c r="V55" s="14" t="n">
         <f aca="false">U55/E55</f>
-        <v>301136.21626423</v>
+        <v>320318.463339889</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="S56" s="26" t="n">
         <f aca="false">IF(D56="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A56-38-1))</f>
-        <v>575678.115283025</v>
+        <v>629610.676491735</v>
       </c>
       <c r="T56" s="26" t="n">
         <f aca="false">IF(C56=สมมติฐาน!$B$8,$AA$7,0)+IF(C56=65,$AA$9,0)+IF(A56=57,$AA$10+$AA$11,0)</f>
@@ -7228,11 +7228,11 @@
       </c>
       <c r="U56" s="26" t="n">
         <f aca="false">G56+H56+I56+J56+K56+L56+P56+Q56+R56+S56+T56</f>
-        <v>755803.191241108</v>
+        <v>809735.752449817</v>
       </c>
       <c r="V56" s="26" t="n">
         <f aca="false">U56/E56</f>
-        <v>297989.285249812</v>
+        <v>319253.187747874</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="S57" s="14" t="n">
         <f aca="false">IF(D57="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A57-38-1))</f>
-        <v>575678.115283025</v>
+        <v>635906.783256652</v>
       </c>
       <c r="T57" s="14" t="n">
         <f aca="false">IF(C57=สมมติฐาน!$B$8,$AA$7,0)+IF(C57=65,$AA$9,0)+IF(A57=57,$AA$10+$AA$11,0)</f>
@@ -7317,11 +7317,11 @@
       </c>
       <c r="U57" s="14" t="n">
         <f aca="false">G57+H57+I57+J57+K57+L57+P57+Q57+R57+S57+T57</f>
-        <v>876860.108361793</v>
+        <v>937088.77633542</v>
       </c>
       <c r="V57" s="14" t="n">
         <f aca="false">U57/E57</f>
-        <v>338939.409332119</v>
+        <v>362220.054617693</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="S58" s="26" t="n">
         <f aca="false">IF(D58="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A58-38-1))</f>
-        <v>575678.115283025</v>
+        <v>642265.851089219</v>
       </c>
       <c r="T58" s="26" t="n">
         <f aca="false">IF(C58=สมมติฐาน!$B$8,$AA$7,0)+IF(C58=65,$AA$9,0)+IF(A58=57,$AA$10+$AA$11,0)</f>
@@ -7406,11 +7406,11 @@
       </c>
       <c r="U58" s="26" t="n">
         <f aca="false">G58+H58+I58+J58+K58+L58+P58+Q58+R58+S58+T58</f>
-        <v>889027.860882175</v>
+        <v>955615.596688369</v>
       </c>
       <c r="V58" s="26" t="n">
         <f aca="false">U58/E58</f>
-        <v>336904.611071526</v>
+        <v>362138.595540425</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="S59" s="14" t="n">
         <f aca="false">IF(D59="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A59-38-1))</f>
-        <v>575678.115283025</v>
+        <v>648688.509600111</v>
       </c>
       <c r="T59" s="14" t="n">
         <f aca="false">IF(C59=สมมติฐาน!$B$8,$AA$7,0)+IF(C59=65,$AA$9,0)+IF(A59=57,$AA$10+$AA$11,0)</f>
@@ -7495,11 +7495,11 @@
       </c>
       <c r="U59" s="14" t="n">
         <f aca="false">G59+H59+I59+J59+K59+L59+P59+Q59+R59+S59+T59</f>
-        <v>901687.190604381</v>
+        <v>974697.584921466</v>
       </c>
       <c r="V59" s="14" t="n">
         <f aca="false">U59/E59</f>
-        <v>335001.932266256</v>
+        <v>362127.329440137</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="S60" s="26" t="n">
         <f aca="false">IF(D60="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A60-38-1))</f>
-        <v>575678.115283025</v>
+        <v>655175.394696112</v>
       </c>
       <c r="T60" s="26" t="n">
         <f aca="false">IF(C60=สมมติฐาน!$B$8,$AA$7,0)+IF(C60=65,$AA$9,0)+IF(A60=57,$AA$10+$AA$11,0)</f>
@@ -7584,11 +7584,11 @@
       </c>
       <c r="U60" s="26" t="n">
         <f aca="false">G60+H60+I60+J60+K60+L60+P60+Q60+R60+S60+T60</f>
-        <v>914857.957247364</v>
+        <v>994355.23666045</v>
       </c>
       <c r="V60" s="26" t="n">
         <f aca="false">U60/E60</f>
-        <v>333230.626767756</v>
+        <v>362186.95603756</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="S61" s="14" t="n">
         <f aca="false">IF(D61="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A61-38-1))</f>
-        <v>575678.115283025</v>
+        <v>661727.148643073</v>
       </c>
       <c r="T61" s="14" t="n">
         <f aca="false">IF(C61=สมมติฐาน!$B$8,$AA$7,0)+IF(C61=65,$AA$9,0)+IF(A61=57,$AA$10+$AA$11,0)</f>
@@ -7673,11 +7673,11 @@
       </c>
       <c r="U61" s="14" t="n">
         <f aca="false">G61+H61+I61+J61+K61+L61+P61+Q61+R61+S61+T61</f>
-        <v>928560.822862723</v>
+        <v>1014609.85622277</v>
       </c>
       <c r="V61" s="14" t="n">
         <f aca="false">U61/E61</f>
-        <v>331589.999946421</v>
+        <v>362318.19595116</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="S62" s="26" t="n">
         <f aca="false">IF(D62="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A62-38-1))</f>
-        <v>575678.115283025</v>
+        <v>668344.420129504</v>
       </c>
       <c r="T62" s="26" t="n">
         <f aca="false">IF(C62=สมมติฐาน!$B$8,$AA$7,0)+IF(C62=65,$AA$9,0)+IF(A62=57,$AA$10+$AA$11,0)</f>
@@ -7762,11 +7762,11 @@
       </c>
       <c r="U62" s="26" t="n">
         <f aca="false">G62+H62+I62+J62+K62+L62+P62+Q62+R62+S62+T62</f>
-        <v>942817.284248943</v>
+        <v>1035483.58909542</v>
       </c>
       <c r="V62" s="26" t="n">
         <f aca="false">U62/E62</f>
-        <v>330079.408419182</v>
+        <v>362521.791047416</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="S63" s="14" t="n">
         <f aca="false">IF(D63="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A63-38-1))</f>
-        <v>575678.115283025</v>
+        <v>675027.864330799</v>
       </c>
       <c r="T63" s="14" t="n">
         <f aca="false">IF(C63=สมมติฐาน!$B$8,$AA$7,0)+IF(C63=65,$AA$9,0)+IF(A63=57,$AA$10+$AA$11,0)</f>
@@ -7851,11 +7851,11 @@
       </c>
       <c r="U63" s="14" t="n">
         <f aca="false">G63+H63+I63+J63+K63+L63+P63+Q63+R63+S63+T63</f>
-        <v>957649.706675166</v>
+        <v>1056999.45572294</v>
       </c>
       <c r="V63" s="14" t="n">
         <f aca="false">U63/E63</f>
-        <v>328698.259797206</v>
+        <v>362798.504798762</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="S64" s="26" t="n">
         <f aca="false">IF(D64="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A64-38-1))</f>
-        <v>575678.115283025</v>
+        <v>681778.142974107</v>
       </c>
       <c r="T64" s="26" t="n">
         <f aca="false">IF(C64=สมมติฐาน!$B$8,$AA$7,0)+IF(C64=65,$AA$9,0)+IF(A64=57,$AA$10+$AA$11,0)</f>
@@ -7940,11 +7940,11 @@
       </c>
       <c r="U64" s="26" t="n">
         <f aca="false">G64+H64+I64+J64+K64+L64+P64+Q64+R64+S64+T64</f>
-        <v>973081.358967409</v>
+        <v>1079181.38665849</v>
       </c>
       <c r="V64" s="26" t="n">
         <f aca="false">U64/E64</f>
-        <v>327446.012453581</v>
+        <v>363149.122649347</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="S65" s="14" t="n">
         <f aca="false">IF(D65="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A65-38-1))</f>
-        <v>575678.115283025</v>
+        <v>688595.924403848</v>
       </c>
       <c r="T65" s="14" t="n">
         <f aca="false">IF(C65=สมมติฐาน!$B$8,$AA$7,0)+IF(C65=65,$AA$9,0)+IF(A65=57,$AA$10+$AA$11,0)</f>
@@ -8029,11 +8029,11 @@
       </c>
       <c r="U65" s="14" t="n">
         <f aca="false">G65+H65+I65+J65+K65+L65+P65+Q65+R65+S65+T65</f>
-        <v>2072251.26704058</v>
+        <v>2185169.0761614</v>
       </c>
       <c r="V65" s="14" t="n">
         <f aca="false">U65/E65</f>
-        <v>683648.389707111</v>
+        <v>720900.666784953</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="S66" s="27" t="n">
         <f aca="false">SUM(S9:S65)</f>
-        <v>10937884.1903775</v>
+        <v>11980376.8364861</v>
       </c>
       <c r="T66" s="27" t="n">
         <f aca="false">SUM(T9:T65)</f>
@@ -8086,11 +8086,11 @@
       </c>
       <c r="U66" s="27" t="n">
         <f aca="false">SUM(U9:U65)</f>
-        <v>38744669.4630376</v>
+        <v>39787162.1091462</v>
       </c>
       <c r="V66" s="27" t="n">
         <f aca="false">SUM(V9:V65)</f>
-        <v>20505315.2221562</v>
+        <v>20890788.3967058</v>
       </c>
     </row>
   </sheetData>
@@ -8173,7 +8173,7 @@
         <v>160</v>
       </c>
       <c r="AA5" s="14" t="n">
-        <f aca="false">MAX(0,สมมติฐาน!$B$44-AA4)</f>
+        <f aca="false">MAX(0,สมมติฐาน!$B$44*(1+สมมติฐาน!$B$39)^(สมมติฐาน!$C$10-1)-AA4)</f>
         <v>0</v>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="S45" s="14" t="n">
         <f aca="false">IF(D45="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A45-35-1))</f>
-        <v>775907.723867545</v>
+        <v>783666.80110622</v>
       </c>
       <c r="T45" s="14" t="n">
         <f aca="false">IF(C45=สมมติฐาน!$C$8,$AA$7,0)+IF(C45=65,$AA$9,0)+IF(A45=58,$AA$10+$AA$11,0)</f>
@@ -11577,11 +11577,11 @@
       </c>
       <c r="U45" s="14" t="n">
         <f aca="false">G45+H45+I45+J45+K45+L45+P45+Q45+R45+S45+T45</f>
-        <v>1008931.58487043</v>
+        <v>1016690.66210911</v>
       </c>
       <c r="V45" s="14" t="n">
         <f aca="false">U45/E45</f>
-        <v>494601.620025072</v>
+        <v>498405.299312842</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="S46" s="26" t="n">
         <f aca="false">IF(D46="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A46-35-1))</f>
-        <v>775907.723867545</v>
+        <v>791503.469117282</v>
       </c>
       <c r="T46" s="26" t="n">
         <f aca="false">IF(C46=สมมติฐาน!$C$8,$AA$7,0)+IF(C46=65,$AA$9,0)+IF(A46=58,$AA$10+$AA$11,0)</f>
@@ -11666,11 +11666,11 @@
       </c>
       <c r="U46" s="26" t="n">
         <f aca="false">G46+H46+I46+J46+K46+L46+P46+Q46+R46+S46+T46</f>
-        <v>1018345.74885495</v>
+        <v>1033941.49410468</v>
       </c>
       <c r="V46" s="26" t="n">
         <f aca="false">U46/E46</f>
-        <v>489428.099168132</v>
+        <v>496923.584823443</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="S47" s="14" t="n">
         <f aca="false">IF(D47="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A47-35-1))</f>
-        <v>775907.723867545</v>
+        <v>799418.503808455</v>
       </c>
       <c r="T47" s="14" t="n">
         <f aca="false">IF(C47=สมมติฐาน!$C$8,$AA$7,0)+IF(C47=65,$AA$9,0)+IF(A47=58,$AA$10+$AA$11,0)</f>
@@ -11755,11 +11755,11 @@
       </c>
       <c r="U47" s="14" t="n">
         <f aca="false">G47+H47+I47+J47+K47+L47+P47+Q47+R47+S47+T47</f>
-        <v>1028140.24506444</v>
+        <v>1051651.02500535</v>
       </c>
       <c r="V47" s="14" t="n">
         <f aca="false">U47/E47</f>
-        <v>484446.510899101</v>
+        <v>495524.489186175</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="S48" s="26" t="n">
         <f aca="false">IF(D48="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A48-35-1))</f>
-        <v>775907.723867545</v>
+        <v>807412.68884654</v>
       </c>
       <c r="T48" s="26" t="n">
         <f aca="false">IF(C48=สมมติฐาน!$C$8,$AA$7,0)+IF(C48=65,$AA$9,0)+IF(A48=58,$AA$10+$AA$11,0)</f>
@@ -11844,11 +11844,11 @@
       </c>
       <c r="U48" s="26" t="n">
         <f aca="false">G48+H48+I48+J48+K48+L48+P48+Q48+R48+S48+T48</f>
-        <v>1038330.43892079</v>
+        <v>1069835.40389979</v>
       </c>
       <c r="V48" s="26" t="n">
         <f aca="false">U48/E48</f>
-        <v>479654.901653952</v>
+        <v>494208.56425708</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="S49" s="14" t="n">
         <f aca="false">IF(D49="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A49-35-1))</f>
-        <v>775907.723867545</v>
+        <v>815486.815735005</v>
       </c>
       <c r="T49" s="14" t="n">
         <f aca="false">IF(C49=สมมติฐาน!$C$8,$AA$7,0)+IF(C49=65,$AA$9,0)+IF(A49=58,$AA$10+$AA$11,0)</f>
@@ -11933,11 +11933,11 @@
       </c>
       <c r="U49" s="14" t="n">
         <f aca="false">G49+H49+I49+J49+K49+L49+P49+Q49+R49+S49+T49</f>
-        <v>1348932.31660894</v>
+        <v>1388511.4084764</v>
       </c>
       <c r="V49" s="14" t="n">
         <f aca="false">U49/E49</f>
-        <v>610918.516925806</v>
+        <v>628843.508274315</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="S50" s="26" t="n">
         <f aca="false">IF(D50="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A50-35-1))</f>
-        <v>775907.723867545</v>
+        <v>823641.683892355</v>
       </c>
       <c r="T50" s="26" t="n">
         <f aca="false">IF(C50=สมมติฐาน!$C$8,$AA$7,0)+IF(C50=65,$AA$9,0)+IF(A50=58,$AA$10+$AA$11,0)</f>
@@ -12022,11 +12022,11 @@
       </c>
       <c r="U50" s="26" t="n">
         <f aca="false">G50+H50+I50+J50+K50+L50+P50+Q50+R50+S50+T50</f>
-        <v>1059962.5101557</v>
+        <v>1107696.47018051</v>
       </c>
       <c r="V50" s="26" t="n">
         <f aca="false">U50/E50</f>
-        <v>470634.177750194</v>
+        <v>491828.543411049</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="S51" s="14" t="n">
         <f aca="false">IF(D51="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A51-35-1))</f>
-        <v>775907.723867545</v>
+        <v>831878.100731279</v>
       </c>
       <c r="T51" s="14" t="n">
         <f aca="false">IF(C51=สมมติฐาน!$C$8,$AA$7,0)+IF(C51=65,$AA$9,0)+IF(A51=58,$AA$10+$AA$11,0)</f>
@@ -12111,11 +12111,11 @@
       </c>
       <c r="U51" s="14" t="n">
         <f aca="false">G51+H51+I51+J51+K51+L51+P51+Q51+R51+S51+T51</f>
-        <v>1071438.32352174</v>
+        <v>1127408.70038547</v>
       </c>
       <c r="V51" s="14" t="n">
         <f aca="false">U51/E51</f>
-        <v>466401.525552799</v>
+        <v>490765.661669573</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="S52" s="26" t="n">
         <f aca="false">IF(D52="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A52-35-1))</f>
-        <v>775907.723867545</v>
+        <v>840196.881738592</v>
       </c>
       <c r="T52" s="26" t="n">
         <f aca="false">IF(C52=สมมติฐาน!$C$8,$AA$7,0)+IF(C52=65,$AA$9,0)+IF(A52=58,$AA$10+$AA$11,0)</f>
@@ -12200,11 +12200,11 @@
       </c>
       <c r="U52" s="26" t="n">
         <f aca="false">G52+H52+I52+J52+K52+L52+P52+Q52+R52+S52+T52</f>
-        <v>1083377.75974777</v>
+        <v>1147666.91761881</v>
       </c>
       <c r="V52" s="26" t="n">
         <f aca="false">U52/E52</f>
-        <v>462351.775914445</v>
+        <v>489788.379671793</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="S53" s="14" t="n">
         <f aca="false">IF(D53="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A53-35-1))</f>
-        <v>775907.723867545</v>
+        <v>848598.850555977</v>
       </c>
       <c r="T53" s="14" t="n">
         <f aca="false">IF(C53=สมมติฐาน!$C$8,$AA$7,0)+IF(C53=65,$AA$9,0)+IF(A53=58,$AA$10+$AA$11,0)</f>
@@ -12289,11 +12289,11 @@
       </c>
       <c r="U53" s="14" t="n">
         <f aca="false">G53+H53+I53+J53+K53+L53+P53+Q53+R53+S53+T53</f>
-        <v>1095799.54919733</v>
+        <v>1168490.67588576</v>
       </c>
       <c r="V53" s="14" t="n">
         <f aca="false">U53/E53</f>
-        <v>458483.340698018</v>
+        <v>488897.361791227</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="S54" s="26" t="n">
         <f aca="false">IF(D54="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A54-35-1))</f>
-        <v>775907.723867545</v>
+        <v>857084.839061537</v>
       </c>
       <c r="T54" s="26" t="n">
         <f aca="false">IF(C54=สมมติฐาน!$C$8,$AA$7,0)+IF(C54=65,$AA$9,0)+IF(A54=58,$AA$10+$AA$11,0)</f>
@@ -12378,11 +12378,11 @@
       </c>
       <c r="U54" s="26" t="n">
         <f aca="false">G54+H54+I54+J54+K54+L54+P54+Q54+R54+S54+T54</f>
-        <v>1310789.70523504</v>
+        <v>1391966.82042903</v>
       </c>
       <c r="V54" s="26" t="n">
         <f aca="false">U54/E54</f>
-        <v>537681.745850346</v>
+        <v>570980.338939902</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12459,7 +12459,7 @@
       </c>
       <c r="S55" s="14" t="n">
         <f aca="false">IF(D55="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A55-35-1))</f>
-        <v>775907.723867545</v>
+        <v>865655.687452153</v>
       </c>
       <c r="T55" s="14" t="n">
         <f aca="false">IF(C55=สมมติฐาน!$C$8,$AA$7,0)+IF(C55=65,$AA$9,0)+IF(A55=58,$AA$10+$AA$11,0)</f>
@@ -12467,11 +12467,11 @@
       </c>
       <c r="U55" s="14" t="n">
         <f aca="false">G55+H55+I55+J55+K55+L55+P55+Q55+R55+S55+T55</f>
-        <v>1332398.93728228</v>
+        <v>1422146.90086689</v>
       </c>
       <c r="V55" s="14" t="n">
         <f aca="false">U55/E55</f>
-        <v>535829.199745904</v>
+        <v>571921.677877457</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="S56" s="26" t="n">
         <f aca="false">IF(D56="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A56-35-1))</f>
-        <v>775907.723867545</v>
+        <v>874312.244326674</v>
       </c>
       <c r="T56" s="26" t="n">
         <f aca="false">IF(C56=สมมติฐาน!$C$8,$AA$7,0)+IF(C56=65,$AA$9,0)+IF(A56=58,$AA$10+$AA$11,0)</f>
@@ -12556,11 +12556,11 @@
       </c>
       <c r="U56" s="26" t="n">
         <f aca="false">G56+H56+I56+J56+K56+L56+P56+Q56+R56+S56+T56</f>
-        <v>1354881.18230424</v>
+        <v>1453285.70276337</v>
       </c>
       <c r="V56" s="26" t="n">
         <f aca="false">U56/E56</f>
-        <v>534186.782739401</v>
+        <v>572984.571709853</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="S57" s="14" t="n">
         <f aca="false">IF(D57="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A57-35-1))</f>
-        <v>775907.723867545</v>
+        <v>883055.366769941</v>
       </c>
       <c r="T57" s="14" t="n">
         <f aca="false">IF(C57=สมมติฐาน!$C$8,$AA$7,0)+IF(C57=65,$AA$9,0)+IF(A57=58,$AA$10+$AA$11,0)</f>
@@ -12645,11 +12645,11 @@
       </c>
       <c r="U57" s="14" t="n">
         <f aca="false">G57+H57+I57+J57+K57+L57+P57+Q57+R57+S57+T57</f>
-        <v>1378271.71002508</v>
+        <v>1485419.35292748</v>
       </c>
       <c r="V57" s="14" t="n">
         <f aca="false">U57/E57</f>
-        <v>532753.850745737</v>
+        <v>574170.444396594</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="S58" s="26" t="n">
         <f aca="false">IF(D58="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A58-35-1))</f>
-        <v>775907.723867545</v>
+        <v>891885.92043764</v>
       </c>
       <c r="T58" s="26" t="n">
         <f aca="false">IF(C58=สมมติฐาน!$C$8,$AA$7,0)+IF(C58=65,$AA$9,0)+IF(A58=58,$AA$10+$AA$11,0)</f>
@@ -12734,11 +12734,11 @@
       </c>
       <c r="U58" s="26" t="n">
         <f aca="false">G58+H58+I58+J58+K58+L58+P58+Q58+R58+S58+T58</f>
-        <v>1402607.21506584</v>
+        <v>1518585.41163594</v>
       </c>
       <c r="V58" s="26" t="n">
         <f aca="false">U58/E58</f>
-        <v>531529.841830797</v>
+        <v>575480.758250281</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="S59" s="14" t="n">
         <f aca="false">IF(D59="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A59-35-1))</f>
-        <v>775907.723867545</v>
+        <v>900804.779642017</v>
       </c>
       <c r="T59" s="14" t="n">
         <f aca="false">IF(C59=สมมติฐาน!$C$8,$AA$7,0)+IF(C59=65,$AA$9,0)+IF(A59=58,$AA$10+$AA$11,0)</f>
@@ -12823,11 +12823,11 @@
       </c>
       <c r="U59" s="14" t="n">
         <f aca="false">G59+H59+I59+J59+K59+L59+P59+Q59+R59+S59+T59</f>
-        <v>1427925.87451026</v>
+        <v>1552822.93028473</v>
       </c>
       <c r="V59" s="14" t="n">
         <f aca="false">U59/E59</f>
-        <v>530514.275991085</v>
+        <v>576917.014606868</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="S60" s="26" t="n">
         <f aca="false">IF(D60="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A60-35-1))</f>
-        <v>775907.723867545</v>
+        <v>909812.827438437</v>
       </c>
       <c r="T60" s="26" t="n">
         <f aca="false">IF(C60=สมมติฐาน!$C$8,$AA$7,0)+IF(C60=65,$AA$9,0)+IF(A60=58,$AA$10+$AA$11,0)</f>
@@ -12912,11 +12912,11 @@
       </c>
       <c r="U60" s="26" t="n">
         <f aca="false">G60+H60+I60+J60+K60+L60+P60+Q60+R60+S60+T60</f>
-        <v>1454267.40779622</v>
+        <v>1588172.51136711</v>
       </c>
       <c r="V60" s="26" t="n">
         <f aca="false">U60/E60</f>
-        <v>529706.754965487</v>
+        <v>578480.754510276</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="S61" s="14" t="n">
         <f aca="false">IF(D61="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A61-35-1))</f>
-        <v>775907.723867545</v>
+        <v>918910.955712821</v>
       </c>
       <c r="T61" s="14" t="n">
         <f aca="false">IF(C61=สมมติฐาน!$C$8,$AA$7,0)+IF(C61=65,$AA$9,0)+IF(A61=58,$AA$10+$AA$11,0)</f>
@@ -13001,11 +13001,11 @@
       </c>
       <c r="U61" s="14" t="n">
         <f aca="false">G61+H61+I61+J61+K61+L61+P61+Q61+R61+S61+T61</f>
-        <v>1481673.13902694</v>
+        <v>1624676.37087222</v>
       </c>
       <c r="V61" s="14" t="n">
         <f aca="false">U61/E61</f>
-        <v>529106.962079091</v>
+        <v>580173.559411642</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="S62" s="26" t="n">
         <f aca="false">IF(D62="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A62-35-1))</f>
-        <v>775907.723867545</v>
+        <v>928100.06526995</v>
       </c>
       <c r="T62" s="26" t="n">
         <f aca="false">IF(C62=สมมติฐาน!$C$8,$AA$7,0)+IF(C62=65,$AA$9,0)+IF(A62=58,$AA$10+$AA$11,0)</f>
@@ -13090,11 +13090,11 @@
       </c>
       <c r="U62" s="26" t="n">
         <f aca="false">G62+H62+I62+J62+K62+L62+P62+Q62+R62+S62+T62</f>
-        <v>1510186.06179938</v>
+        <v>1662378.40320178</v>
       </c>
       <c r="V62" s="26" t="n">
         <f aca="false">U62/E62</f>
-        <v>528714.662119</v>
+        <v>581997.051883475</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="S63" s="14" t="n">
         <f aca="false">IF(D63="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A63-35-1))</f>
-        <v>775907.723867545</v>
+        <v>937381.065922649</v>
       </c>
       <c r="T63" s="14" t="n">
         <f aca="false">IF(C63=สมมติฐาน!$C$8,$AA$7,0)+IF(C63=65,$AA$9,0)+IF(A63=58,$AA$10+$AA$11,0)</f>
@@ -13179,11 +13179,11 @@
       </c>
       <c r="U63" s="14" t="n">
         <f aca="false">G63+H63+I63+J63+K63+L63+P63+Q63+R63+S63+T63</f>
-        <v>1539850.90665183</v>
+        <v>1701324.24870693</v>
       </c>
       <c r="V63" s="14" t="n">
         <f aca="false">U63/E63</f>
-        <v>528529.701242094</v>
+        <v>583952.896349024</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="S64" s="26" t="n">
         <f aca="false">IF(D64="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A64-35-1))</f>
-        <v>775907.723867545</v>
+        <v>946754.876581876</v>
       </c>
       <c r="T64" s="26" t="n">
         <f aca="false">IF(C64=สมมติฐาน!$C$8,$AA$7,0)+IF(C64=65,$AA$9,0)+IF(A64=58,$AA$10+$AA$11,0)</f>
@@ -13268,11 +13268,11 @@
       </c>
       <c r="U64" s="26" t="n">
         <f aca="false">G64+H64+I64+J64+K64+L64+P64+Q64+R64+S64+T64</f>
-        <v>1835649.7070259</v>
+        <v>2006496.85974023</v>
       </c>
       <c r="V64" s="26" t="n">
         <f aca="false">U64/E64</f>
-        <v>617703.927105387</v>
+        <v>675194.720017832</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="S65" s="14" t="n">
         <f aca="false">IF(D65="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A65-35-1))</f>
-        <v>775907.723867545</v>
+        <v>956222.425347694</v>
       </c>
       <c r="T65" s="14" t="n">
         <f aca="false">IF(C65=สมมติฐาน!$C$8,$AA$7,0)+IF(C65=65,$AA$9,0)+IF(A65=58,$AA$10+$AA$11,0)</f>
@@ -13357,11 +13357,11 @@
       </c>
       <c r="U65" s="14" t="n">
         <f aca="false">G65+H65+I65+J65+K65+L65+P65+Q65+R65+S65+T65</f>
-        <v>1878463.2831455</v>
+        <v>2058777.98462565</v>
       </c>
       <c r="V65" s="14" t="n">
         <f aca="false">U65/E65</f>
-        <v>619716.54647863</v>
+        <v>679203.471287449</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="S66" s="26" t="n">
         <f aca="false">IF(D66="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A66-35-1))</f>
-        <v>775907.723867545</v>
+        <v>965784.649601171</v>
       </c>
       <c r="T66" s="26" t="n">
         <f aca="false">IF(C66=สมมติฐาน!$C$8,$AA$7,0)+IF(C66=65,$AA$9,0)+IF(A66=58,$AA$10+$AA$11,0)</f>
@@ -13446,11 +13446,11 @@
       </c>
       <c r="U66" s="26" t="n">
         <f aca="false">G66+H66+I66+J66+K66+L66+P66+Q66+R66+S66+T66</f>
-        <v>3556752.76837607</v>
+        <v>3746629.6941097</v>
       </c>
       <c r="V66" s="26" t="n">
         <f aca="false">U66/E66</f>
-        <v>1150386.79466438</v>
+        <v>1211800.08993685</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="S67" s="27" t="n">
         <f aca="false">SUM(S9:S66)</f>
-        <v>17845877.6489535</v>
+        <v>19953477.2229638</v>
       </c>
       <c r="T67" s="27" t="n">
         <f aca="false">SUM(T9:T66)</f>
@@ -13503,11 +13503,11 @@
       </c>
       <c r="U67" s="27" t="n">
         <f aca="false">SUM(U9:U66)</f>
-        <v>65372147.4695873</v>
+        <v>67479747.0435975</v>
       </c>
       <c r="V67" s="27" t="n">
         <f aca="false">SUM(V9:V66)</f>
-        <v>34694342.7067225</v>
+        <v>35479503.9341526</v>
       </c>
     </row>
   </sheetData>
@@ -13590,7 +13590,7 @@
         <v>160</v>
       </c>
       <c r="AA5" s="14" t="n">
-        <f aca="false">MAX(0,สมมติฐาน!$B$44-AA4)</f>
+        <f aca="false">MAX(0,สมมติฐาน!$B$44*(1+สมมติฐาน!$B$39)^(สมมติฐาน!$D$10-1)-AA4)</f>
         <v>0</v>
       </c>
     </row>
@@ -17075,7 +17075,7 @@
       </c>
       <c r="S46" s="26" t="n">
         <f aca="false">IF(D46="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A46-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1127018.51090114</v>
       </c>
       <c r="T46" s="26" t="n">
         <f aca="false">IF(C46=สมมติฐาน!$D$8,$AA$7,0)+IF(C46=65,$AA$9,0)+IF(A46=62,$AA$10+$AA$11,0)</f>
@@ -17083,11 +17083,11 @@
       </c>
       <c r="U46" s="26" t="n">
         <f aca="false">G46+H46+I46+J46+K46+L46+P46+Q46+R46+S46+T46</f>
-        <v>1358297.9367707</v>
+        <v>1369456.53588854</v>
       </c>
       <c r="V46" s="26" t="n">
         <f aca="false">U46/E46</f>
-        <v>652812.836941861</v>
+        <v>658175.781660549</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="S47" s="14" t="n">
         <f aca="false">IF(D47="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A47-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1138288.69601015</v>
       </c>
       <c r="T47" s="14" t="n">
         <f aca="false">IF(C47=สมมติฐาน!$D$8,$AA$7,0)+IF(C47=65,$AA$9,0)+IF(A47=62,$AA$10+$AA$11,0)</f>
@@ -17172,11 +17172,11 @@
       </c>
       <c r="U47" s="14" t="n">
         <f aca="false">G47+H47+I47+J47+K47+L47+P47+Q47+R47+S47+T47</f>
-        <v>1368092.43298019</v>
+        <v>1390521.21720704</v>
       </c>
       <c r="V47" s="14" t="n">
         <f aca="false">U47/E47</f>
-        <v>644627.626363541</v>
+        <v>655195.782132721</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17253,7 +17253,7 @@
       </c>
       <c r="S48" s="26" t="n">
         <f aca="false">IF(D48="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A48-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1149671.58297025</v>
       </c>
       <c r="T48" s="26" t="n">
         <f aca="false">IF(C48=สมมติฐาน!$D$8,$AA$7,0)+IF(C48=65,$AA$9,0)+IF(A48=62,$AA$10+$AA$11,0)</f>
@@ -17261,11 +17261,11 @@
       </c>
       <c r="U48" s="26" t="n">
         <f aca="false">G48+H48+I48+J48+K48+L48+P48+Q48+R48+S48+T48</f>
-        <v>1378282.62683655</v>
+        <v>1412094.2980235</v>
       </c>
       <c r="V48" s="26" t="n">
         <f aca="false">U48/E48</f>
-        <v>636695.210932815</v>
+        <v>652314.452370817</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17342,7 +17342,7 @@
       </c>
       <c r="S49" s="14" t="n">
         <f aca="false">IF(D49="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A49-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1161168.29879995</v>
       </c>
       <c r="T49" s="14" t="n">
         <f aca="false">IF(C49=สมมติฐาน!$D$8,$AA$7,0)+IF(C49=65,$AA$9,0)+IF(A49=62,$AA$10+$AA$11,0)</f>
@@ -17350,11 +17350,11 @@
       </c>
       <c r="U49" s="14" t="n">
         <f aca="false">G49+H49+I49+J49+K49+L49+P49+Q49+R49+S49+T49</f>
-        <v>1388884.5045247</v>
+        <v>1434192.89154135</v>
       </c>
       <c r="V49" s="14" t="n">
         <f aca="false">U49/E49</f>
-        <v>629012.479898532</v>
+        <v>649532.214105876</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17431,7 +17431,7 @@
       </c>
       <c r="S50" s="26" t="n">
         <f aca="false">IF(D50="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A50-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1172779.98178795</v>
       </c>
       <c r="T50" s="26" t="n">
         <f aca="false">IF(C50=สมมติฐาน!$D$8,$AA$7,0)+IF(C50=65,$AA$9,0)+IF(A50=62,$AA$10+$AA$11,0)</f>
@@ -17439,11 +17439,11 @@
       </c>
       <c r="U50" s="26" t="n">
         <f aca="false">G50+H50+I50+J50+K50+L50+P50+Q50+R50+S50+T50</f>
-        <v>1699914.69807145</v>
+        <v>1756834.7680761</v>
       </c>
       <c r="V50" s="26" t="n">
         <f aca="false">U50/E50</f>
-        <v>754779.48371477</v>
+        <v>780052.576005729</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="S51" s="14" t="n">
         <f aca="false">IF(D51="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A51-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1184507.78160583</v>
       </c>
       <c r="T51" s="14" t="n">
         <f aca="false">IF(C51=สมมติฐาน!$D$8,$AA$7,0)+IF(C51=65,$AA$9,0)+IF(A51=62,$AA$10+$AA$11,0)</f>
@@ -17528,11 +17528,11 @@
       </c>
       <c r="U51" s="14" t="n">
         <f aca="false">G51+H51+I51+J51+K51+L51+P51+Q51+R51+S51+T51</f>
-        <v>1411390.51143749</v>
+        <v>1480038.38126002</v>
       </c>
       <c r="V51" s="14" t="n">
         <f aca="false">U51/E51</f>
-        <v>614384.116410447</v>
+        <v>644266.817549919</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17609,7 +17609,7 @@
       </c>
       <c r="S52" s="26" t="n">
         <f aca="false">IF(D52="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A52-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1196352.85942189</v>
       </c>
       <c r="T52" s="26" t="n">
         <f aca="false">IF(C52=สมมติฐาน!$D$8,$AA$7,0)+IF(C52=65,$AA$9,0)+IF(A52=62,$AA$10+$AA$11,0)</f>
@@ -17617,11 +17617,11 @@
       </c>
       <c r="U52" s="26" t="n">
         <f aca="false">G52+H52+I52+J52+K52+L52+P52+Q52+R52+S52+T52</f>
-        <v>1423329.94766352</v>
+        <v>1503822.89530211</v>
       </c>
       <c r="V52" s="26" t="n">
         <f aca="false">U52/E52</f>
-        <v>607432.747343512</v>
+        <v>641784.622259195</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17698,7 +17698,7 @@
       </c>
       <c r="S53" s="14" t="n">
         <f aca="false">IF(D53="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A53-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1208316.38801611</v>
       </c>
       <c r="T53" s="14" t="n">
         <f aca="false">IF(C53=สมมติฐาน!$D$8,$AA$7,0)+IF(C53=65,$AA$9,0)+IF(A53=62,$AA$10+$AA$11,0)</f>
@@ -17706,11 +17706,11 @@
       </c>
       <c r="U53" s="14" t="n">
         <f aca="false">G53+H53+I53+J53+K53+L53+P53+Q53+R53+S53+T53</f>
-        <v>1435751.73711308</v>
+        <v>1528208.21334589</v>
       </c>
       <c r="V53" s="14" t="n">
         <f aca="false">U53/E53</f>
-        <v>600719.587197103</v>
+        <v>639403.445137576</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17787,7 +17787,7 @@
       </c>
       <c r="S54" s="26" t="n">
         <f aca="false">IF(D54="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A54-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1220399.55189627</v>
       </c>
       <c r="T54" s="26" t="n">
         <f aca="false">IF(C54=สมมติฐาน!$D$8,$AA$7,0)+IF(C54=65,$AA$9,0)+IF(A54=62,$AA$10+$AA$11,0)</f>
@@ -17795,11 +17795,11 @@
       </c>
       <c r="U54" s="26" t="n">
         <f aca="false">G54+H54+I54+J54+K54+L54+P54+Q54+R54+S54+T54</f>
-        <v>1448675.36685641</v>
+        <v>1553215.00696937</v>
       </c>
       <c r="V54" s="26" t="n">
         <f aca="false">U54/E54</f>
-        <v>594242.003359399</v>
+        <v>637123.829469277</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17876,7 +17876,7 @@
       </c>
       <c r="S55" s="14" t="n">
         <f aca="false">IF(D55="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A55-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1232603.54741523</v>
       </c>
       <c r="T55" s="14" t="n">
         <f aca="false">IF(C55=สมมติฐาน!$D$8,$AA$7,0)+IF(C55=65,$AA$9,0)+IF(A55=62,$AA$10+$AA$11,0)</f>
@@ -17884,11 +17884,11 @@
       </c>
       <c r="U55" s="14" t="n">
         <f aca="false">G55+H55+I55+J55+K55+L55+P55+Q55+R55+S55+T55</f>
-        <v>1672351.12519804</v>
+        <v>1789094.76082997</v>
       </c>
       <c r="V55" s="14" t="n">
         <f aca="false">U55/E55</f>
-        <v>672542.239441295</v>
+        <v>719491.127725218</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="S56" s="26" t="n">
         <f aca="false">IF(D56="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A56-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1244929.58288938</v>
       </c>
       <c r="T56" s="26" t="n">
         <f aca="false">IF(C56=สมมติฐาน!$D$8,$AA$7,0)+IF(C56=65,$AA$9,0)+IF(A56=62,$AA$10+$AA$11,0)</f>
@@ -17973,11 +17973,11 @@
       </c>
       <c r="U56" s="26" t="n">
         <f aca="false">G56+H56+I56+J56+K56+L56+P56+Q56+R56+S56+T56</f>
-        <v>1694833.37022</v>
+        <v>1823903.04132608</v>
       </c>
       <c r="V56" s="26" t="n">
         <f aca="false">U56/E56</f>
-        <v>668219.174597627</v>
+        <v>719107.262245381</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18054,7 +18054,7 @@
       </c>
       <c r="S57" s="14" t="n">
         <f aca="false">IF(D57="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A57-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1257378.87871828</v>
       </c>
       <c r="T57" s="14" t="n">
         <f aca="false">IF(C57=สมมติฐาน!$D$8,$AA$7,0)+IF(C57=65,$AA$9,0)+IF(A57=62,$AA$10+$AA$11,0)</f>
@@ -18062,11 +18062,11 @@
       </c>
       <c r="U57" s="14" t="n">
         <f aca="false">G57+H57+I57+J57+K57+L57+P57+Q57+R57+S57+T57</f>
-        <v>1718223.89794084</v>
+        <v>1859742.86487581</v>
       </c>
       <c r="V57" s="14" t="n">
         <f aca="false">U57/E57</f>
-        <v>664158.156489096</v>
+        <v>718860.559534715</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="S58" s="26" t="n">
         <f aca="false">IF(D58="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A58-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1269952.66750546</v>
       </c>
       <c r="T58" s="26" t="n">
         <f aca="false">IF(C58=สมมติฐาน!$D$8,$AA$7,0)+IF(C58=65,$AA$9,0)+IF(A58=62,$AA$10+$AA$11,0)</f>
@@ -18151,11 +18151,11 @@
       </c>
       <c r="U58" s="26" t="n">
         <f aca="false">G58+H58+I58+J58+K58+L58+P58+Q58+R58+S58+T58</f>
-        <v>1742559.4029816</v>
+        <v>1896652.15870376</v>
       </c>
       <c r="V58" s="26" t="n">
         <f aca="false">U58/E58</f>
-        <v>660357.592559581</v>
+        <v>718752.342847832</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18232,7 +18232,7 @@
       </c>
       <c r="S59" s="14" t="n">
         <f aca="false">IF(D59="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A59-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1282652.19418051</v>
       </c>
       <c r="T59" s="14" t="n">
         <f aca="false">IF(C59=สมมติฐาน!$D$8,$AA$7,0)+IF(C59=65,$AA$9,0)+IF(A59=62,$AA$10+$AA$11,0)</f>
@@ -18240,11 +18240,11 @@
       </c>
       <c r="U59" s="14" t="n">
         <f aca="false">G59+H59+I59+J59+K59+L59+P59+Q59+R59+S59+T59</f>
-        <v>1767878.06242601</v>
+        <v>1934670.34482323</v>
       </c>
       <c r="V59" s="14" t="n">
         <f aca="false">U59/E59</f>
-        <v>656815.992391853</v>
+        <v>718783.975826011</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="S60" s="26" t="n">
         <f aca="false">IF(D60="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A60-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1295478.71612232</v>
       </c>
       <c r="T60" s="26" t="n">
         <f aca="false">IF(C60=สมมติฐาน!$D$8,$AA$7,0)+IF(C60=65,$AA$9,0)+IF(A60=62,$AA$10+$AA$11,0)</f>
@@ -18329,11 +18329,11 @@
       </c>
       <c r="U60" s="26" t="n">
         <f aca="false">G60+H60+I60+J60+K60+L60+P60+Q60+R60+S60+T60</f>
-        <v>1794219.59571198</v>
+        <v>1973838.400051</v>
       </c>
       <c r="V60" s="26" t="n">
         <f aca="false">U60/E60</f>
-        <v>653531.967123103</v>
+        <v>718956.863168448</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="S61" s="14" t="n">
         <f aca="false">IF(D61="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A61-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1308433.50328354</v>
       </c>
       <c r="T61" s="14" t="n">
         <f aca="false">IF(C61=สมมติฐาน!$D$8,$AA$7,0)+IF(C61=65,$AA$9,0)+IF(A61=62,$AA$10+$AA$11,0)</f>
@@ -18418,11 +18418,11 @@
       </c>
       <c r="U61" s="14" t="n">
         <f aca="false">G61+H61+I61+J61+K61+L61+P61+Q61+R61+S61+T61</f>
-        <v>1821625.3269427</v>
+        <v>2014198.91844294</v>
       </c>
       <c r="V61" s="14" t="n">
         <f aca="false">U61/E61</f>
-        <v>650504.228900283</v>
+        <v>719272.451318263</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18499,7 +18499,7 @@
       </c>
       <c r="S62" s="26" t="n">
         <f aca="false">IF(D62="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A62-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1321517.83831638</v>
       </c>
       <c r="T62" s="26" t="n">
         <f aca="false">IF(C62=สมมติฐาน!$D$8,$AA$7,0)+IF(C62=65,$AA$9,0)+IF(A62=62,$AA$10+$AA$11,0)</f>
@@ -18507,11 +18507,11 @@
       </c>
       <c r="U62" s="26" t="n">
         <f aca="false">G62+H62+I62+J62+K62+L62+P62+Q62+R62+S62+T62</f>
-        <v>1850138.24971514</v>
+        <v>2055796.17624821</v>
       </c>
       <c r="V62" s="26" t="n">
         <f aca="false">U62/E62</f>
-        <v>647731.590375071</v>
+        <v>719732.229163561</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="S63" s="14" t="n">
         <f aca="false">IF(D63="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A63-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1334733.01669954</v>
       </c>
       <c r="T63" s="14" t="n">
         <f aca="false">IF(C63=สมมติฐาน!$D$8,$AA$7,0)+IF(C63=65,$AA$9,0)+IF(A63=62,$AA$10+$AA$11,0)</f>
@@ -18596,11 +18596,11 @@
       </c>
       <c r="U63" s="14" t="n">
         <f aca="false">G63+H63+I63+J63+K63+L63+P63+Q63+R63+S63+T63</f>
-        <v>1879803.09456758</v>
+        <v>2098676.19948382</v>
       </c>
       <c r="V63" s="14" t="n">
         <f aca="false">U63/E63</f>
-        <v>645212.964238242</v>
+        <v>720337.728753814</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18677,7 +18677,7 @@
       </c>
       <c r="S64" s="26" t="n">
         <f aca="false">IF(D64="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A64-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1348080.34686654</v>
       </c>
       <c r="T64" s="26" t="n">
         <f aca="false">IF(C64=สมมติฐาน!$D$8,$AA$7,0)+IF(C64=65,$AA$9,0)+IF(A64=62,$AA$10+$AA$11,0)</f>
@@ -18685,11 +18685,11 @@
       </c>
       <c r="U64" s="26" t="n">
         <f aca="false">G64+H64+I64+J64+K64+L64+P64+Q64+R64+S64+T64</f>
-        <v>1910666.39915207</v>
+        <v>2142886.8342353</v>
       </c>
       <c r="V64" s="26" t="n">
         <f aca="false">U64/E64</f>
-        <v>642947.36279327</v>
+        <v>721090.526031883</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="S65" s="14" t="n">
         <f aca="false">IF(D65="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A65-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1361561.1503352</v>
       </c>
       <c r="T65" s="14" t="n">
         <f aca="false">IF(C65=สมมติฐาน!$D$8,$AA$7,0)+IF(C65=65,$AA$9,0)+IF(A65=62,$AA$10+$AA$11,0)</f>
@@ -18774,11 +18774,11 @@
       </c>
       <c r="U65" s="14" t="n">
         <f aca="false">G65+H65+I65+J65+K65+L65+P65+Q65+R65+S65+T65</f>
-        <v>2218415.47106126</v>
+        <v>2464116.70961316</v>
       </c>
       <c r="V65" s="14" t="n">
         <f aca="false">U65/E65</f>
-        <v>731868.856163509</v>
+        <v>812927.20017646</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18855,7 +18855,7 @@
       </c>
       <c r="S66" s="26" t="n">
         <f aca="false">IF(D66="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A66-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1375176.76183855</v>
       </c>
       <c r="T66" s="26" t="n">
         <f aca="false">IF(C66=สมมติฐาน!$D$8,$AA$7,0)+IF(C66=65,$AA$9,0)+IF(A66=62,$AA$10+$AA$11,0)</f>
@@ -18863,11 +18863,11 @@
       </c>
       <c r="U66" s="26" t="n">
         <f aca="false">G66+H66+I66+J66+K66+L66+P66+Q66+R66+S66+T66</f>
-        <v>2262958.71565608</v>
+        <v>2522275.56571134</v>
       </c>
       <c r="V66" s="26" t="n">
         <f aca="false">U66/E66</f>
-        <v>731925.436737629</v>
+        <v>815798.199160115</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="S67" s="14" t="n">
         <f aca="false">IF(D67="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A67-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1388928.52945694</v>
       </c>
       <c r="T67" s="14" t="n">
         <f aca="false">IF(C67=สมมติฐาน!$D$8,$AA$7,0)+IF(C67=65,$AA$9,0)+IF(A67=62,$AA$10+$AA$11,0)</f>
@@ -18952,11 +18952,11 @@
       </c>
       <c r="U67" s="14" t="n">
         <f aca="false">G67+H67+I67+J67+K67+L67+P67+Q67+R67+S67+T67</f>
-        <v>2309301.50733255</v>
+        <v>2582370.12500618</v>
       </c>
       <c r="V67" s="14" t="n">
         <f aca="false">U67/E67</f>
-        <v>732269.046894783</v>
+        <v>818857.868564813</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19033,7 +19033,7 @@
       </c>
       <c r="S68" s="26" t="n">
         <f aca="false">IF(D68="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A68-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1402817.81475151</v>
       </c>
       <c r="T68" s="26" t="n">
         <f aca="false">IF(C68=สมมติฐาน!$D$8,$AA$7,0)+IF(C68=65,$AA$9,0)+IF(A68=62,$AA$10+$AA$11,0)</f>
@@ -19041,11 +19041,11 @@
       </c>
       <c r="U68" s="26" t="n">
         <f aca="false">G68+H68+I68+J68+K68+L68+P68+Q68+R68+S68+T68</f>
-        <v>2357516.54779273</v>
+        <v>2644474.45076094</v>
       </c>
       <c r="V68" s="26" t="n">
         <f aca="false">U68/E68</f>
-        <v>732899.821384052</v>
+        <v>822108.695029944</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19122,7 +19122,7 @@
       </c>
       <c r="S69" s="14" t="n">
         <f aca="false">IF(D69="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A69-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1416845.99289902</v>
       </c>
       <c r="T69" s="14" t="n">
         <f aca="false">IF(C69=สมมติฐาน!$D$8,$AA$7,0)+IF(C69=65,$AA$9,0)+IF(A69=62,$AA$10+$AA$11,0)</f>
@@ -19130,11 +19130,11 @@
       </c>
       <c r="U69" s="14" t="n">
         <f aca="false">G69+H69+I69+J69+K69+L69+P69+Q69+R69+S69+T69</f>
-        <v>2407679.47588752</v>
+        <v>2708665.55700324</v>
       </c>
       <c r="V69" s="14" t="n">
         <f aca="false">U69/E69</f>
-        <v>733818.007567982</v>
+        <v>825553.227543066</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="S70" s="26" t="n">
         <f aca="false">IF(D70="รับราชการ",0,$AA$6*12*(1+สมมติฐาน!$B$41)^(A70-36-1))</f>
-        <v>1115859.9117833</v>
+        <v>1431014.45282801</v>
       </c>
       <c r="T70" s="26" t="n">
         <f aca="false">IF(C70=สมมติฐาน!$D$8,$AA$7,0)+IF(C70=65,$AA$9,0)+IF(A70=62,$AA$10+$AA$11,0)</f>
@@ -19219,11 +19219,11 @@
       </c>
       <c r="U70" s="26" t="n">
         <f aca="false">G70+H70+I70+J70+K70+L70+P70+Q70+R70+S70+T70</f>
-        <v>5028483.74368141</v>
+        <v>5343638.28472612</v>
       </c>
       <c r="V70" s="26" t="n">
         <f aca="false">U70/E70</f>
-        <v>1502541.83554099</v>
+        <v>1596711.94858459</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="S71" s="27" t="n">
         <f aca="false">SUM(S9:S70)</f>
-        <v>29012357.7063659</v>
+        <v>32946468.5572993</v>
       </c>
       <c r="T71" s="27" t="n">
         <f aca="false">SUM(T9:T70)</f>
@@ -19276,11 +19276,11 @@
       </c>
       <c r="U71" s="27" t="n">
         <f aca="false">SUM(U9:U70)</f>
-        <v>95391398.5032325</v>
+        <v>99325509.3541659</v>
       </c>
       <c r="V71" s="27" t="n">
         <f aca="false">SUM(V9:V70)</f>
-        <v>48208515.4016329</v>
+        <v>49590656.7626383</v>
       </c>
     </row>
   </sheetData>
@@ -19605,15 +19605,15 @@
       </c>
       <c r="B23" s="30" t="n">
         <f aca="false">SUM(1_ชั้นผู้น้อย!S47:S65)</f>
-        <v>10937884.1903775</v>
+        <v>11980376.8364861</v>
       </c>
       <c r="C23" s="30" t="n">
         <f aca="false">SUM(2_ระดับกลาง!S44:S66)</f>
-        <v>17845877.6489535</v>
+        <v>19953477.2229638</v>
       </c>
       <c r="D23" s="30" t="n">
         <f aca="false">SUM(3_ระดับสูง!S45:S70)</f>
-        <v>29012357.7063659</v>
+        <v>32946468.5572993</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>214</v>
@@ -19665,15 +19665,15 @@
       </c>
       <c r="B26" s="27" t="n">
         <f aca="false">SUM(B23:B25)</f>
-        <v>17230551.6510164</v>
+        <v>18273044.297125</v>
       </c>
       <c r="C26" s="27" t="n">
         <f aca="false">SUM(C23:C25)</f>
-        <v>32416859.3595337</v>
+        <v>34524458.933544</v>
       </c>
       <c r="D26" s="27" t="n">
         <f aca="false">SUM(D23:D25)</f>
-        <v>48898157.5213078</v>
+        <v>52832268.3722412</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19874,15 +19874,15 @@
       </c>
       <c r="B42" s="15" t="n">
         <f aca="false">B40/B45</f>
-        <v>0.0531913901275034</v>
+        <v>0.0517976834617177</v>
       </c>
       <c r="C42" s="15" t="n">
         <f aca="false">C40/C45</f>
-        <v>0.0661526548679597</v>
+        <v>0.0640865044550175</v>
       </c>
       <c r="D42" s="15" t="n">
         <f aca="false">D40/D45</f>
-        <v>0.0474597567641771</v>
+        <v>0.0455799582584091</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>239</v>
@@ -19903,15 +19903,15 @@
       </c>
       <c r="B45" s="31" t="n">
         <f aca="false">SUM(1_ชั้นผู้น้อย!U9:U65)</f>
-        <v>38744669.4630376</v>
+        <v>39787162.1091462</v>
       </c>
       <c r="C45" s="31" t="n">
         <f aca="false">SUM(2_ระดับกลาง!U9:U66)</f>
-        <v>65372147.4695873</v>
+        <v>67479747.0435975</v>
       </c>
       <c r="D45" s="31" t="n">
         <f aca="false">SUM(3_ระดับสูง!U9:U70)</f>
-        <v>95391398.5032325</v>
+        <v>99325509.3541659</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>242</v>
@@ -19923,15 +19923,15 @@
       </c>
       <c r="B46" s="31" t="n">
         <f aca="false">SUM(1_ชั้นผู้น้อย!V9:V65)</f>
-        <v>20505315.2221562</v>
+        <v>20890788.3967058</v>
       </c>
       <c r="C46" s="31" t="n">
         <f aca="false">SUM(2_ระดับกลาง!V9:V66)</f>
-        <v>34694342.7067225</v>
+        <v>35479503.9341526</v>
       </c>
       <c r="D46" s="31" t="n">
         <f aca="false">SUM(3_ระดับสูง!V9:V70)</f>
-        <v>48208515.4016329</v>
+        <v>49590656.7626383</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>244</v>
@@ -19969,15 +19969,15 @@
       </c>
       <c r="B50" s="14" t="n">
         <f aca="false">B45-B49</f>
-        <v>-1255330.5369624</v>
+        <v>-212837.890853807</v>
       </c>
       <c r="C50" s="14" t="n">
         <f aca="false">C45-C49</f>
-        <v>25372147.4695873</v>
+        <v>27479747.0435975</v>
       </c>
       <c r="D50" s="14" t="n">
         <f aca="false">D45-D49</f>
-        <v>55391398.5032325</v>
+        <v>59325509.3541659</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19986,15 +19986,15 @@
       </c>
       <c r="B51" s="14" t="n">
         <f aca="false">B46-B49</f>
-        <v>-19494684.7778438</v>
+        <v>-19109211.6032942</v>
       </c>
       <c r="C51" s="14" t="n">
         <f aca="false">C46-C49</f>
-        <v>-5305657.29327751</v>
+        <v>-4520496.06584738</v>
       </c>
       <c r="D51" s="14" t="n">
         <f aca="false">D46-D49</f>
-        <v>8208515.40163289</v>
+        <v>9590656.76263832</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20064,11 +20064,11 @@
       </c>
       <c r="B59" s="33" t="n">
         <f aca="false">C45*สมมติฐาน!$B$50/1000000000000</f>
-        <v>111.132650698298</v>
+        <v>114.715569974116</v>
       </c>
       <c r="C59" s="33" t="n">
         <f aca="false">C46*สมมติฐาน!$B$50/1000000000000</f>
-        <v>58.9803826014282</v>
+        <v>60.3151566880595</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>260</v>
@@ -20080,11 +20080,11 @@
       </c>
       <c r="B60" s="33" t="n">
         <f aca="false">B59/60</f>
-        <v>1.85221084497164</v>
+        <v>1.91192616623526</v>
       </c>
       <c r="C60" s="33" t="n">
         <f aca="false">C59/60</f>
-        <v>0.983006376690471</v>
+        <v>1.00525261146766</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>262</v>
@@ -20120,10 +20120,10 @@
         <v>0</v>
       </c>
       <c r="B65" s="35" t="n">
-        <v>37275966</v>
+        <v>38392526</v>
       </c>
       <c r="C65" s="35" t="n">
-        <v>37275966</v>
+        <v>38392526</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20131,10 +20131,10 @@
         <v>0.01</v>
       </c>
       <c r="B66" s="35" t="n">
-        <v>49051404</v>
+        <v>50587703</v>
       </c>
       <c r="C66" s="35" t="n">
-        <v>35881141</v>
+        <v>36815244</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20142,10 +20142,10 @@
         <v>0.02</v>
       </c>
       <c r="B67" s="37" t="n">
-        <v>65372147</v>
+        <v>67479747</v>
       </c>
       <c r="C67" s="37" t="n">
-        <v>34694343</v>
+        <v>35479504</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20153,10 +20153,10 @@
         <v>0.03</v>
       </c>
       <c r="B68" s="35" t="n">
-        <v>88216767</v>
+        <v>91099760</v>
       </c>
       <c r="C68" s="35" t="n">
-        <v>33691324</v>
+        <v>34354385</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20205,7 +20205,7 @@
       <c r="D75" s="40"/>
       <c r="E75" s="40"/>
     </row>
-    <row r="76" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="40" t="s">
         <v>272</v>
       </c>
@@ -20214,7 +20214,7 @@
       <c r="D76" s="40"/>
       <c r="E76" s="40"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="40" t="s">
         <v>273</v>
       </c>
